--- a/data_extactor/batch_10_fa/batch_0070_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0070_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3M Post-it App | ADP Workforce Now | Adobe Acrobat | Adobe InDesign | Alpha Software Alpha Five | نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار صدور صورتحساب | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | نرم‌افزار حسابداری | نرم‌افزار ورود اطلاعات | نرم‌افزار پایگاه داده | Dropbox | سیستم‌های تبادل الکترونیکی داده EDI | Evernote | Facebook | FileMaker Pro | نرم‌افزار سیستم بایگانی | Google Docs | Google Drive | Google Sites | نرم‌افزار Google Workspace | GroupMe | Henry Schein Dentrix | IBM Check Processing Control System CPSC | IBM Notes | Intuit QuickBooks | LexisNexis | LinkedIn | نرم‌افزار MEDITECH | Mavenlink | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری فرآیندهای پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Propertyware | نرم‌افزار مدیریت سوابق | نرم‌افزار SAP | Sage 50 Accounting | Salesforce.com Salesforce CRM | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | St. Paul Travelers e-CARMA | نرم‌افزار سیستم پیاده‌سازی صوتی | نرم‌افزار مرورگر وب | Yardi software</t>
+          <t>3M Post-it App | ADP Workforce Now | Adobe Acrobat | Adobe InDesign | Alpha Software Alpha Five | نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار صدور صورتحساب | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | نرم‌افزار حسابداری | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | Dropbox | سیستم‌های تبادل الکترونیکی داده EDI | Evernote | Facebook | FileMaker Pro | نرم‌افزار سیستم بایگانی | Google Docs | Google Drive | Google Sites | نرم‌افزار Google Workspace | GroupMe | Henry Schein Dentrix | IBM Check Processing Control System CPSC | IBM Notes | Intuit QuickBooks | LexisNexis | LinkedIn | نرم‌افزار MEDITECH | Mavenlink | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Publisher | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Propertyware | نرم‌افزار مدیریت سوابق | نرم‌افزار SAP | Sage 50 Accounting | Salesforce.com Salesforce CRM | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | St. Paul Travelers e-CARMA | نرم‌افزار سیستم پیاده‌سازی صوتی | نرم‌افزار مرورگر وب | نرم‌افزار Yardi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخن‌گفتن | نگارش | تفکر انتقادی</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>امور دفتری | زبان انگلیسی | خدمات مشتریان و شخصی | امور اداری و مدیریت</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | حساسیت به مشکلات | ترتیب‌دهی به اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان به صورت نشسته | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار وظایف یکسان | فشار زمانی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی</t>
+          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارمندان صدور صورتحساب و ارسال | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | کارمندان مکاتبات | نمایندگان خدمات مشتریان | متخصصان مدیریت اسناد | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | منشی‌های حقوقی و دستیاران اداری | تحلیلگران مدیریت | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | اپراتورهای تلفنخانه، شامل خدمات پاسخگویی | پردازشگرهای واژه و تایپیست‌ها</t>
+          <t>مدیران خدمات اداری | کارمندان صدور صورتحساب و ثبت | کارمندان دفترداری، حسابداری و حسابرسی | کارمندان کارگزاری | کارمندان مکاتبات | نمایندگان خدمات مشتریان | متخصصان مدیریت اسناد | منشی‌های اجرایی و دستیاران اداری اجرایی | کارمندان بایگانی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | متصدیان پذیرش و کارمندان اطلاعات | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | اپراتورهای تلفنخانه، شامل سرویس پاسخگویی | واژه‌پردازان و تایپیست‌ها</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن‌گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و شخصی | تولید و فرآوری | رایانه‌ها و الکترونیک</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | تولید و فرآوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | درک کتبی | ترتیب‌دهی به اطلاعات | بیان شفاهی | درک شفاهی | ثبات بازو-دست | توجه انتخابی | حساسیت به مشکلات</t>
+          <t>بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | ثبات دست و بازو | توجه انتخابی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | فشار زمانی | مکالمات تلفنی | ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | آزادی در تصمیم‌گیری</t>
+          <t>ایمیل | فشار زمانی | مکالمات تلفنی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | آزادی در تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | اپراتورهای ابزار کنترل عددی رایانه‌ای | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | واردکنندگان داده‌ها | کارمندان بایگانی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارمندان پست و اپراتورهای ماشین‌های پست، به جز خدمات پستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات کالاهای کاغذی | کارکنان فرآیندهای عکاسی و اپراتورهای ماشین‌های پردازش | مرتب‌کنندگان، پردازشگران و اپراتورهای ماشین‌های پردازش نامه‌های خدمات پستی | تکنسین‌ها و کارکنان پیش از چاپ | کارکنان صحافی و تکمیل چاپ | اپراتورهای ماشین چاپ | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارمندان ارسال، دریافت و موجودی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | اپراتورهای ابزار کنترل عددی کامپیوتری | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | اپراتورهای ورود داده | کارمندان بایگانی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | دسته‌بندی‌کنندگان، پردازش‌کنندگان و اپراتورهای ماشین‌های پردازش خدمات پستی | تکنسین‌ها و کارگران پیش از چاپ | کارکنان صحافی و پرداخت چاپ | اپراتورهای ماشین چاپ | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارمندان ارسال، دریافت و موجودی کالا</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,27 +622,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | سخن‌گفتن | گوش دادن فعال | تفکر انتقادی</t>
+          <t>درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ارتباطات و رسانه | رایانه‌ها و الکترونیک</t>
+          <t>زبان انگلیسی | ارتباطات و رسانه | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | بینایی نزدیک | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مشکلات | سرعت ادراکی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی به اطلاعات</t>
+          <t>درک کتبی | بینایی نزدیک | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | سرعت ادراکی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا درست بودن | صرف زمان به صورت نشسته | داخل ساختمان، محیط کنترل‌شده | ارتباط با دیگران | فشار زمانی | ایمیل | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویز که مزاحم یا ناراحت‌کننده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | فراوانی تصمیم‌گیری</t>
+          <t>اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | فشار زمانی | ایمیل | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>آرشیویست‌ها | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | واردکنندگان داده‌ها | ناشران رومیزی | متخصصان مدیریت اسناد | ویراستاران | کارمندان بایگانی | ویراستاران فیلم و ویدئو | کتابداران و متخصصان مجموعه‌های رسانه‌ای | تکنسین‌های کتابخانه | پیاده‌سازان صداهای پزشکی | تحلیلگران اخبار، خبرنگاران و روزنامه‌نگاران | اپراتورهای ماشین‌های اداری، به جز رایانه | شاعران، ترانه‌سرایان و نویسندگان خلاق | دستیاران پژوهشی علوم اجتماعی | دستیاران آماری | نویسندگان فنی | پردازشگرهای واژه و تایپیست‌ها | نویسندگان و پدیدآورندگان</t>
+          <t>آرشیوچی‌ها | کارمندان مکاتبات | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | اپراتورهای ورود داده | ناشران رومیزی | متخصصان مدیریت اسناد | ویراستاران | کارمندان بایگانی | تدوینگران فیلم و ویدئو | کتابداران و متخصصان مجموعه‌های رسانه‌ای | تکنسین‌های کتابخانه | نسخه‌نویسان پزشکی | تحلیلگران اخبار، گزارشگران و روزنامه‌نگاران | اپراتورهای ماشین‌های اداری، به جز رایانه | شاعران، ترانه‌سرایان و نویسندگان خلاق | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری | نویسندگان فنی | واژه‌پردازان و تایپیست‌ها | نویسندگان و مؤلفان</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,32 +674,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>زبان برنامه‌نویسی APL | Avidian Technologies Prophet | Benfield ReMetrica | Bentley MicroStation | C# | C++ | Corel WordPerfect Office Suite | نرم‌افزار بصری‌سازی داده‌ها | نرم‌افزار پایگاه داده | GGY AXIS | نرم‌افزار Google Workspace | Harvard Graphics | Hyland OnBase Enterprise Content Management | IBM Lotus 1-2-3 | IBM SPSS Statistics | Insightful S-PLUS | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Word | Minitab | Oracle Java | Oracle PL/SQL | PolySystems Asset Delphi | Python | QSR International NVivo | R | SAP BusinessObjects Crystal Reports | SAS | STATISTICA | ابزارهای توسعه نرم‌افزار | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Systat Software SigmaStat | Tableau | The MathWorks MATLAB | Towers Perrin MoSes | نرم‌افزار مرورگر وب | Wolfram Research Mathematica | dBASE</t>
+          <t>زبان برنامه‌نویسی APL | Avidian Technologies Prophet | Benfield ReMetrica | Bentley MicroStation | C# | C++ | Corel WordPerfect Office Suite | نرم‌افزار تجسم داده | نرم‌افزار پایگاه داده | GGY AXIS | نرم‌افزار Google Workspace | Harvard Graphics | Hyland OnBase Enterprise Content Management | IBM Lotus 1-2-3 | IBM SPSS Statistics | Insightful S-PLUS | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Visual Studio | Microsoft Word | Minitab | Oracle Java | Oracle PL/SQL | PolySystems Asset Delphi | Python | QSR International NVivo | R | SAP BusinessObjects Crystal Reports | SAS | STATISTICA | ابزارهای توسعه نرم‌افزار | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Systat Software SigmaStat | Tableau | The MathWorks MATLAB | Towers Perrin MoSes | نرم‌افزار مرورگر وب | Wolfram Research Mathematica | dBASE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | گوش دادن فعال | سخن‌گفتن | نظارت</t>
+          <t>ریاضیات | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | گوش دادن فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ریاضیات | رایانه‌ها و الکترونیک | خدمات مشتریان و شخصی | آموزش و پرورش | امور اداری</t>
+          <t>زبان انگلیسی | ریاضیات | رایانه و الکترونیک | خدمات مشتری و شخصی | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | درک کتبی | سهولت در کار با اعداد | درک شفاهی | بیان کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی به اطلاعات | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | حساسیت به مشکلات | روان بودن ایده‌ها | سرعت ادراکی | سرعت بستار | اصالت</t>
+          <t>استدلال ریاضی | درک کتبی | توانایی عددی | درک شفاهی | بیان کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | حساسیت به مسئله | روانی ایده‌ها | سرعت ادراکی | سرعت بستار | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان به صورت نشسته | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | داخل ساختمان، محیط کنترل‌شده | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | فشار زمانی</t>
+          <t>ایمیل | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | فشار زمانی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیوانفورماتیک | زیست‌شناسان آمار | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران هوش تجاری | مدیران داده‌های بالینی | تحلیلگران سیستم‌های رایانه‌ای | واردکنندگان داده‌ها | دانشمندان داده‌ها | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | کارمندان بایگانی | تحلیلگران کمی مالی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیلگران مدیریت | متخصصان مدارک پزشکی | تحلیلگران تحقیق در عملیات | دستیاران پژوهشی علوم اجتماعی | آمارشناسان | پژوهشگران نظرسنجی</t>
+          <t>تکنسین‌های بیوانفورماتیک | آمارشناسان زیستی | کارمندان دفترداری، حسابداری و حسابرسی | تحلیلگران هوش تجاری | مدیران داده‌های بالینی | تحلیلگران سیستم‌های کامپیوتری | اپراتورهای ورود داده | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | کارمندان بایگانی | تحلیلگران کمی مالی | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیل‌گران مدیریت | متخصصان مدارک پزشکی | تحلیل‌گران تحقیق در عملیات | دستیاران تحقیقات علوم اجتماعی | آمارشناسان | پژوهشگران نظرسنجی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | سخن‌گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>امور اداری و مدیریت | زبان انگلیسی | خدمات مشتریان و شخصی | رایانه‌ها و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مشکلات | ترتیب‌دهی به اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اشتراک زمانی | چالاکی انگشتان | چالاکی دست | بینایی دور | حفظ کردن | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار وظایف یکسان</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارمندان دفتری عمومی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | منشی‌های اجرایی و دستیاران اداری اجرایی | منشی‌های پزشکی و دستیاران اداری | منشی‌های حقوقی و دستیاران اداری | واردکنندگان داده‌ها | پردازشگرهای واژه و تایپیست‌ها | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان خدمات مشتریان | کارمندان بایگانی | کارمندان مکاتبات | کارمندان پست و اپراتورهای ماشین‌های پست، به جز خدمات پستی | اپراتورهای ماشین‌های اداری، به جز رایانه | مصححان و نشانه‌گذاران کپی | دستیاران آماری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارمندان ارسال، دریافت و موجودی | کارمندان اطلاعات و سوابق، همه موارد دیگر | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری</t>
+          <t>کارمندان دفتری عمومی | منشی‌ها و دستیاران اداری، به جز حقوقی، پزشکی و اجرایی | منشی‌های اجرایی و دستیاران اداری اجرایی | منشی‌های پزشکی و دستیاران اداری | منشی‌های حقوقی و دستیاران اداری | اپراتورهای ورود داده | واژه‌پردازان و تایپیست‌ها | متصدیان پذیرش و کارمندان اطلاعات | نمایندگان خدمات مشتریان | کارمندان بایگانی | کارمندان مکاتبات | کارمندان پست و اپراتورهای ماشین‌های پست، به جز اداره پست | اپراتورهای ماشین‌های اداری، به جز رایانه | مصححان و نشانه‌گذاران کپی | دستیاران آماری | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | کارمندان تولید، برنامه‌ریزی و هماهنگی | کارمندان ارسال، دریافت و موجودی کالا | کارمندان اطلاعات و ثبت سوابق، سایر | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن‌گفتن | درک مطلب | گوش دادن فعال | استراتژی‌های یادگیری | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | گوش دادن فعال | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>امور اداری و مدیریت | تولید و فرآوری | خدمات مشتریان و شخصی | زبان انگلیسی | مکانیک | آموزش و پرورش | زیست‌شناسی | تولید مواد غذایی | ریاضیات</t>
+          <t>مدیریت و اداره | تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | آموزش و پرورش | زیست‌شناسی | تولید مواد غذایی | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مشکلات | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | وضوح گفتار | بینایی دور | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی | ثبات بازو-دست | دقت کنترل | چالاکی دست | تجسم فضایی | سرعت ادراکی | انعطاف‌پذیری بستار | روان بودن ایده‌ها</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | وضوح گفتار | بینایی دور | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی | ثبات دست و بازو | دقت کنترل | مهارت دستی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فضای باز، در معرض همه شرایط آب و هوایی | آزادی در تصمیم‌گیری | ارتباط با دیگران | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | فشار زمانی | قرار گرفتن در معرض دمای بسیار گرم یا سرد | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | ارتباط با دیگران | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | پیامدهای کاری و نتایج سایر کارکنان | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | کشاورزان، دامداران و سایر مدیران کشاورزی | سرپرستان خط اول مشاغل ساختمانی و استخراج | سرپرستان خط اول کارکنان سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌کاران، کارگران و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارکنان خانه‌داری و سرایداری | سرپرستان خط اول کارکنان فضای سبز، خدمات چمن و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول همراهان مسافر | سرپرستان خط اول کارکنان تولید و عملیات | سرپرستان خط اول کارکنان امنیتی | تکنسین‌های جنگل و حفاظت | مدیران عمومی و عملیاتی | مدیران تولید صنعتی | مدیران مرتع | هماهنگ‌کنندگان بازیافت</t>
+          <t>تکنسین‌های کشاورزی | کشاورزان، دامداران و سایر مدیران کشاورزی | سرپرستان خط اول مشاغل ساختمانی و کارگران استخراج | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط مقدم کارکنان تهیه و سرو غذا | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول کارگران فضای سبز، خدمات چمن‌زنی و نگهداری محوطه | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان رده اول کارگران تولید و بهره‌برداری | سرپرستان خط اول کارکنان امنیتی | تکنسین‌های جنگل و حفاظت | مدیران عمومی و عملیات | مدیران تولید صنعتی | مدیران مراتع | هماهنگ‌کنندگان بازیافت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن‌گفتن | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | امور اداری و مدیریت | قانون و حکومت | امور اداری | امنیت و ایمنی عمومی | ریاضیات | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | اداری | ایمنی و امنیت عمومی | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مشکلات | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان شفاهی | درک کتبی | انعطاف‌پذیری بستار | وضوح گفتار | بینایی دور | سرعت ادراکی | تشخیص گفتار | سرعت بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی به اطلاعات | بیان کتبی | توجه شنیداری | توجه انتخابی</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان شفاهی | درک کتبی | انعطاف‌پذیری بستار | وضوح گفتار | بینایی دور | سرعت ادراکی | تشخیص گفتار | سرعت بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی | توجه شنیداری | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا درست بودن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تاثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویز که مزاحم یا ناراحت‌کننده هستند | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | اهمیت تکرار وظایف یکسان | فضای باز، در معرض همه شرایط آب و هوایی | فشار زمانی | داخل ساختمان، محیط غیرکنترل‌شده | قرار گرفتن در معرض دمای بسیار گرم یا سرد | نزدیکی فیزیکی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان به صورت ایستاده | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل</t>
+          <t>اهمیت دقیق یا درست بودن | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | مکالمات تلفنی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای ایستادن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | بازرسان هوانوردی | بازرسان ساختمان و سازه | بازرسان انطباق محیطی | تکنسین‌های علوم و حفاظت محیط زیست، شامل بهداشت | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | تکنسین‌های علوم غذایی | دانشمندان و فن‌آوران مواد غذایی | بازرسان و محققان اموال دولتی | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | مدیران تولید صنعتی | بازرسان، آزمایش‌کنندگان، مرتب‌کنندگان، نمونه‌برداران و توزین‌کنندگان | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | تحلیلگران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | بازرسان حمل و نقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی | توزین‌کنندگان، اندازه‌گیران، بررسی‌کنندگان و نمونه‌برداران، ثبت سوابق</t>
+          <t>تکنسین‌های کشاورزی | بازرسان هوانوردی | بازرسان ساختمان و ساخت‌وساز | بازرسان انطباق زیست‌محیطی | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | تکنسین‌های علوم غذایی | دانشمندان و تکنولوژیست‌های علوم غذایی | بازرسان و محققان اموال دولتی | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | مدیران تولید صنعتی | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Creative Cloud software | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Breedtrak | نرم‌افزار ایمیل | KinTraks | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Questionmark Perception | Respondus | Reudink Software ZooEasy | VSN International GenStat | Winners Programs BirdStud | Winners Programs Uni-Stud</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Breedtrak | نرم‌افزار ایمیل | KinTraks | Microsoft Access | Microsoft Excel | Microsoft Internet Explorer | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Questionmark Perception | Respondus | Reudink Software ZooEasy | VSN International GenStat | Winners Programs BirdStud | Winners Programs Uni-Stud</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | علوم تجربی | سخن‌گفتن | گوش دادن فعال</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | علوم | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | فروش و بازاریابی | امور اداری و مدیریت | زیست‌شناسی | ریاضیات | امور اداری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | زیست‌شناسی | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مشکلات | وضوح گفتار | بینایی دور | قدرت تنه | قدرت ایستا | هماهنگی چندعضوی | چالاکی انگشتان | ثبات بازو-دست | ترتیب‌دهی به اطلاعات | استدلال استقرایی | درک شفاهی</t>
+          <t>بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | بینایی دور | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | مهارت انگشتان | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال استقرایی | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض همه شرایط آب و هوایی | پیامد خطا | فضای باز، زیر سقف</t>
+          <t>آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض تمام شرایط آب و هوایی | پیامد خطا | فضای باز، زیر سقف</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | تکنسین‌های کشاورزی | مراقبان حیوانات | کارکنان کنترل حیوانات | دانشمندان علوم دامی | مربیان حیوانات | خریداران و ماموران خرید محصولات کشاورزی | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران مزارع و کارگران کشاورزی، محصولات زراعی، گلخانه‌ای و نهالستان | کارگران مزارع، دامداری و حیوانات آبزی‌پروری | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | کارکنان ماهیگیری و شکار | دانشمندان و فن‌آوران مواد غذایی | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | سلاخان و بسته‌بندهای گوشت | دانشمندان خاک و گیاه | دامپزشکان | دستیاران دامپزشک و مراقبان حیوانات آزمایشگاهی | فن‌آوران و تکنسین‌های دامپزشکی</t>
+          <t>بازرسان کشاورزی | تکنسین‌های کشاورزی | مراقبان حیوانات | کارکنان کنترل حیوانات | دانشمندان علوم دامی | مربیان حیوانات | خریداران و نمایندگان خرید، محصولات کشاورزی | کشاورزان، دامداران و سایر مدیران کشاورزی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | کارگران کشاورزی، حیوانات مزرعه، دامداری و آبزی‌پروری | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | کارگران ماهیگیری و شکار | دانشمندان و تکنولوژیست‌های علوم غذایی | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | ذبح‌کنندگان و بسته‌بندندگان گوشت | دانشمندان خاک و گیاه | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | گوش دادن فعال | سخن‌گفتن | تفکر انتقادی</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چالاکی دست | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | چالاکی انگشتان | درک شفاهی</t>
+          <t>مهارت دستی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت ایستاده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | داخل ساختمان، محیط کنترل‌شده | فشار زمانی | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | سرعت کار تعیین‌شده توسط سرعت تجهیزات | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت دقیق یا درست بودن</t>
+          <t>صرف زمان برای ایستادن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سرعت تعیین‌شده توسط سرعت تجهیزات | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | اهمیت دقیق یا درست بودن</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | بازرسان کشاورزی | نانواها | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران مزارع و کارگران کشاورزی، محصولات زراعی، گلخانه‌ای و نهالستان | سازندگان دسته‌ای مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | تکنسین‌های علوم غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | درجه‌بندها و اندازه‌گیرهای الوار | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکنی | بسته‌بندها و بسته‌بندی‌کنندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | توزین‌کنندگان، اندازه‌گیران، بررسی‌کنندگان و نمونه‌برداران، ثبت سوابق</t>
+          <t>اپراتورهای تجهیزات کشاورزی | بازرسان کشاورزی | نانوایان | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | بچ‌سازان مواد غذایی | اپراتورها و متصدیان ماشین‌های پخت مواد غذایی | تکنسین‌های علوم غذایی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | درجه‌بندی‌کنندگان و ارزیابان چوب | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌دهندگان و پاک‌کنندگان گوشت، مرغ و ماهی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چندعضوی | بینایی نزدیک | ادراک عمق | بینایی دور | حساسیت به مشکلات | جهت‌گیری پاسخ | کنترل سرعت | زمان عکس‌العمل | درک شفاهی | ثبات بازو-دست | چالاکی دست | بیان شفاهی | حساسیت شنوایی | قدرت تنه | قدرت ایستا | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه‌دار | چالاکی انگشتان | ترتیب‌دهی به اطلاعات | استدلال قیاسی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی نزدیک | درک عمق | بینایی دور | حساسیت به مسئله | جهت‌گیری پاسخ | کنترل نرخ | زمان عکس‌العمل | درک شفاهی | ثبات دست و بازو | مهارت دستی | بیان شفاهی | حساسیت شنوایی | قدرت تنه | قدرت ایستا | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | مهارت انگشتان | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>فضای باز، در معرض همه شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | قرار گرفتن در معرض دمای بسیار گرم یا سرد | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | ارتباط با دیگران | در یک وسیله نقلیه روباز یا کار با تجهیزات روباز | قرار گرفتن در معرض آلاینده‌ها | سرعت کار تعیین‌شده توسط سرعت تجهیزات</t>
+          <t>فضای باز، در معرض تمام شرایط آب و هوایی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | ارتباط با دیگران | در یک وسیله نقلیه روباز یا کار با تجهیزات | قرار گرفتن در معرض آلاینده‌ها | سرعت تعیین‌شده توسط سرعت تجهیزات</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان نوار نقاله | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های خردکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی، الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران مزارع و کارگران کشاورزی، محصولات زراعی، گلخانه‌ای و نهالستان | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون‌های صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده، فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساخت‌وساز | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکنی | بسته‌بندها و بسته‌بندی‌کنندگان دستی | اپراتورهای تجهیزات روسازی، آسفالت و کوبش | جابجا‌کنندگان، سم‌پاشان و اعمال‌کنندگان آفت‌کش‌ها، پوشش گیاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های جداسازی، فیلتر کردن، شفاف‌سازی، رسوب‌دهی و تقطیر | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
+          <t>اپراتورها و متصدیان نوار نقاله | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | کارگران کشاورزی و کارگران ساده، محصول، نهالستان و گلخانه | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | دست‌اندرکاران، سم‌پاش‌ها و اعمال‌کنندگان آفت‌کش، پوشش گیاهی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0070_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0070_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>اداری و دفتری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>اداری | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | تشخیص گفتار | وضوح گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | کارمندان صدور صورت‌حساب و ثبت اسناد | کارمندان دفاتر مالی، حسابداری و حسابرسی | کارمندان کارگزاری | کارمندان مکاتبات و امور اداری | کارشناسان خدمات پس از فروش و امور مشتریان | متخصصان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی (به‌جز حقوق و دستمزد و ثبت زمان) | مصاحبه‌گران (به‌جز ارزیابی صلاحیت و تسهیلات) | مسئولان دفاتر و دستیاران اداری حقوقی | تحلیل‌گران مدیریت | متخصصان اسناد و مدارک پزشکی | مسئولان دفاتر و دستیاران اداری پزشکی | متصدیان پذیرش و کارمندان اطلاعات | مسئولان دفاتر و دستیاران اداری (به‌جز حقوقی، پزشکی و اجرایی) | متصدیان تلفنخانه و پاسخگویی به تماس‌ها | متصدیان تایپ و پردازش متن</t>
+          <t>مدیران خدمات اداری و پشتیبانی | کارمندان صدور صورتحساب و ثبت اسناد مالی | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان امور اداری و معاملات کارگزاری | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مدیریت اسناد و مدارک | مسئولان دفاتر و دستیاران اجرایی مدیریت | متصدیان بایگانی و اسناد | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | متصدیان پذیرش و اطلاعات | منشی‌ها و دستیاران اداری عمومی | اپراتورهای مراکز تلفن و پاسخگویی | تایپیست‌ها و متصدیان حروف‌چینی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | تولید و فرآوری | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | تولید و فرآوری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | ثبات دست و بازو | توجه انتخابی | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | ثبات دست و بازو | توجه انتخابی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های چسب‌زنی و اتصال | تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران و تکنسین‌های دستگاه‌های خودپرداز و فروش خودکار | اپراتورهای ماشین‌ابزار CNC | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | متصدیان ورود اطلاعات (داده‌آمایان) | متصدیان بایگانی | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای بارگذاری و تخلیه ماشین‌آلات | کارمندان امور پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی | تنظیم‌کنندگان و اپراتورهای دستگاه‌های فرز و صفحه تراش فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌ابزارهای چندکاره | تنظیم‌کنندگان و اپراتورهای دستگاه‌های تولید محصولات کاغذی | کارگران و اپراتورهای فرآوری و چاپ عکس | متصدیان تفکیک، پردازش و اپراتورهای دستگاه‌های پستی | تکنسین‌ها و کارکنان پیش از چاپ | صحافان و کارگران تکمیلی چاپ | اپراتورهای ماشین‌آلات چاپ | کارمندان برنامه‌ریزی، تولید و پیگیری سفارش‌ها | کارمندان انبارداری، ارسال و دریافت کالا</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تعمیرکاران دوربین و تجهیزات عکاسی | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | اپراتورهای ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | متصدیان ورود اطلاعات و داده‌آمایی | متصدیان بایگانی و اسناد | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | اپراتورها و متصدیان تفکیک و پردازش پستی | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | کارگران صحافی و تکمیل چاپ | اپراتورهای ماشین‌های چاپ | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارمندان انبار، ارسال و دریافت کالا</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | سخن گفتن | شنیدن فعال | تفکر انتقادی</t>
+          <t>درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | دید نزدیک | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | سرعت ادراک | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | بینایی نزدیک | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | سرعت ادراکی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>آرشیوداران | کارمندان مکاتبات و امور اداری | گزارش‌نویسان دادگاه و پیاده‌سازان هم‌زمان گفتار | متصدیان ورود اطلاعات (داده‌آمایان) | متخصصان نشر رومیزی | متخصصان مدیریت اسناد و مدارک | ویراستاران | متصدیان بایگانی | تدوین‌گران فیلم و ویدئو | کتابداران و متخصصان مجموعه‌های رسانه‌ای | تکنسین‌های کتابداری | پیاده‌سازان متون پزشکی | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | شاعران، ترانه‌سرایان و نویسندگان خلاق | دستیاران پژوهشی علوم اجتماعی | دستیاران آمار | نویسندگان متون فنی | متصدیان تایپ و پردازش متن | نویسندگان و پدیدآورندگان متون</t>
+          <t>کارشناسان اسناد و آرشیو | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | متصدیان ورود اطلاعات و داده‌آمایی | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | کارشناسان مدیریت اسناد و مدارک | ویراستاران | متصدیان بایگانی و اسناد | تدوین‌گران فیلم و ویدیو | کتابداران و کارشناسان مجموعه‌های رسانه‌ای | تکنسین‌های کتابداری | پیاده‌سازان و تایپیست‌های متون پزشکی | تحلیل‌گران خبر، خبرنگاران و روزنامه‌نگاران | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | شاعران، ترانه‌سرایان و نویسندگان خلاق | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار | نویسندگان متون فنی | تایپیست‌ها و متصدیان حروف‌چینی | نویسندگان و پدیدآورندگان</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | شنیدن فعال | سخن گفتن | نظارت</t>
+          <t>ریاضیات | درک مطلب | تفکر انتقادی | یادگیری فعال | نگارش | گوش دادن فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ریاضیات | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | آموزش و تدریس | اداری و دفتری</t>
+          <t>زبان انگلیسی | ریاضیات | رایانه و الکترونیک | خدمات مشتری و شخصی | آموزش و پرورش | اداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | درک کتبی | کار با اعداد و محاسبات | درک شفاهی | بیان کتبی | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در دسته‌بندی | درک روابط کل و جزء | توجه انتخابی | حساسیت به مسئله | روانی کلام و سیالی ایده‌ها | سرعت ادراک | تفکیک سریع الگوها | خلاقیت و نوآوری</t>
+          <t>استدلال ریاضی | درک کتبی | توانایی عددی | درک شفاهی | بیان کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توجه انتخابی | حساسیت به مسئله | روانی ایده‌ها | سرعت ادراکی | سرعت بستار | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیوانفورماتیک | زیست‌آمارشناسان | کارمندان دفاتر مالی، حسابداری و حسابرسی | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های رایانه‌ای | متصدیان ورود اطلاعات (داده‌آمایان) | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد و مدارک | متصدیان بایگانی | تحلیل‌گران داده‌های مالی و محاسبات کمی | متخصصان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | تحلیل‌گران مدیریت | متخصصان اسناد و مدارک پزشکی | تحلیل‌گران تحقیق در عملیات | دستیاران پژوهشی علوم اجتماعی | کارشناسان آمار | پژوهشگران آمارگیری و پیمایش</t>
+          <t>تکنسین‌های بیوانفورماتیک | کارشناسان آمار زیستی | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | تحلیل‌گران سیستم‌های کامپیوتری | متصدیان ورود اطلاعات و داده‌آمایی | دانشمندان داده | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | متصدیان بایگانی و اسناد | تحلیل‌گران کمّی مالی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | تحلیل‌گران تحقیق در عملیات | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | کارشناسان آمار | پژوهشگران پیمایشی و افکارسنجی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
+          <t>مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری در دسته‌بندی | تقسیم توجه | چابکی انگشتان | چابکی دستی | دید دور | حافظه و یادآوری | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | درک کتبی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تقسیم توجه | مهارت انگشتان | مهارت دستی | بینایی دور | حفظ کردن | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>متصدیان امور دفتری و امور عمومی اداری | مسئولان دفاتر و دستیاران اداری (به‌جز حقوقی، پزشکی و اجرایی) | مسئولان دفاتر و دستیاران اجرایی مدیریت | مسئولان دفاتر و دستیاران اداری پزشکی | مسئولان دفاتر و دستیاران اداری حقوقی | متصدیان ورود اطلاعات (داده‌آمایان) | متصدیان تایپ و پردازش متن | متصدیان پذیرش و کارمندان اطلاعات | کارشناسان خدمات پس از فروش و امور مشتریان | متصدیان بایگانی | کارمندان مکاتبات و امور اداری | کارمندان امور پستی و اپراتورهای ماشین‌های تمبر و بسته‌بندی | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | ویراستاران فنی و نمونه‌خوان‌ها | دستیاران و تکنسین‌های آمار | دستیاران منابع انسانی (به‌جز حقوق و دستمزد و ثبت زمان) | کارمندان برنامه‌ریزی، تولید و پیگیری سفارش‌ها | کارمندان انبارداری، ارسال و دریافت کالا | کارمندان اطلاعات و اسناد، سایر مشاغل | سرپرستان رده‌اول کارکنان اداری و پشتیبانی</t>
+          <t>متصدیان امور دفتری و امور عمومی اداری | منشی‌ها و دستیاران اداری عمومی | مسئولان دفاتر و دستیاران اجرایی مدیریت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | منشی‌ها و دستیاران اداری دفاتر حقوقی | متصدیان ورود اطلاعات و داده‌آمایی | تایپیست‌ها و متصدیان حروف‌چینی | متصدیان پذیرش و اطلاعات | کارشناسان خدمات و پشتیبانی مشتریان | متصدیان بایگانی و اسناد | کارشناسان مکاتبات و پاسخ‌گویی به شکایات | کارمندان امور مراسلات و متصدیان ماشین‌های پستی، به جز پست دولتی | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | ویراستاران فنی و نمونه‌خوان‌ها | دستیاران و تکنسین‌های آمار | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارمندان انبار، ارسال و دریافت کالا | سایر متصدیان ثبت اسناد و اطلاعات | سرپرستان رده‌اول کارکنان اداری و پشتیبانی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | شنیدن فعال | روش‌های یادگیری | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | درک مطلب | گوش دادن فعال | راهبردهای یادگیری | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | تولید و فرآوری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مکانیک | آموزش و تدریس | زیست‌شناسی | تولید مواد غذایی | ریاضیات</t>
+          <t>مدیریت و اداره | تولید و فرآوری | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | آموزش و پرورش | زیست‌شناسی | تولید مواد غذایی | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | دید نزدیک | وضوح گفتار | دید دور | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی | ثبات دست و بازو | دقت در کنترل | چابکی دستی | تجسم فضایی | سرعت ادراک | تفکیک سریع الگوها | روانی کلام و سیالی ایده‌ها</t>
+          <t>درک شفاهی | حساسیت به مسئله | بیان شفاهی | تشخیص گفتار | بینایی نزدیک | وضوح گفتار | بینایی دور | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی | ثبات دست و بازو | دقت کنترل | مهارت دستی | تجسم | سرعت ادراکی | انعطاف‌پذیری بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | مدیران امور کشاورزی و دامپروری | سرپرستان رده‌اول کارگران مشاغل ساختمانی و استخراج | سرپرستان رده‌اول کارکنان سرگرمی و تفریحی (به‌جز خدمات شرط‌بندی) | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران خدماتی و جابجایی دستی بار | سرپرستان رده‌اول خدمات نظافتی و امور خدماتی اماکن | سرپرستان رده‌اول کارگران فضای سبز، باغبانی و محوطه‌سازی | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل جابه‌جایی مواد | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروش (به‌جز خرده‌فروشی) | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و کارکنان خدمات مسافری | سرپرستان رده‌اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | تکنسین‌های جنگل‌داری و حفاظت از منابع طبیعی | مدیران کل و مدیران عملیاتی | مدیران تولید صنعتی | کارشناسان مدیریت مرتع | هماهنگ‌کنندگان امور بازیافت</t>
+          <t>تکنسین‌های کشاورزی | مدیران امور کشاورزی، دامپروری و شیلات | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول کارکنان آماده‌سازی و سرو غذا | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده اول کارگران تولید و عملیات | سرپرستان رده‌اول کارکنان حراست و انتظامات | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | مدیران کل و مدیران عملیات | مدیران تولید صنعتی | مدیران و کارشناسان مدیریت مراتع | هماهنگ‌کنندگان امور بازیافت</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | حقوق و مقررات دولتی | اداری و دفتری | ایمنی و امنیت عمومی | ریاضیات | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | قانون و دولت | اداری | ایمنی و امنیت عمومی | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | بیان شفاهی | درک کتبی | درک روابط کل و جزء | وضوح گفتار | دید دور | سرعت ادراک | تشخیص گفتار | تفکیک سریع الگوها | انعطاف‌پذیری در دسته‌بندی | مرتب‌سازی اطلاعات | بیان کتبی | توجه شنیداری | توجه انتخابی</t>
+          <t>حساسیت به مسئله | درک شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | بیان شفاهی | درک کتبی | انعطاف‌پذیری بستار | وضوح گفتار | بینایی دور | سرعت ادراکی | تشخیص گفتار | سرعت بستار | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | بیان کتبی | توجه شنیداری | توجه انتخابی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های کشاورزی | بازرسان هوانوردی | بازرسان ساختمان و سازه | بازرسان انطباق زیست‌محیطی | تکنسین‌های علوم و حفاظت از محیط زیست (شامل بهداشت محیط) | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | تکنسین‌های علوم صنایع غذایی | دانشمندان و متخصصان علوم و صنایع غذایی | بازرسان و محققان اموال دولتی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | مهندسان ایمنی و بهداشت حرفه‌ای (به‌جز مهندسان ایمنی معدن) | مدیران تولید صنعتی | بازرسان، آزمون‌گران، درجه‌بندان، نمونه‌برداران و متصدیان توزین | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | بازرسان حمل و نقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های ترابری (به‌جز هوانوردی) | متصدیان توزین، سنجش و نمونه‌برداری</t>
+          <t>تکنسین‌های کشاورزی | بازرسان هوانوردی و فرودگاهی | بازرسان ساخت‌وساز و ساختمان | بازرسان رعایت ضوابط زیست‌محیطی | تکنسین‌های علوم و بهداشت محیط زیست | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | تکنسین‌های علوم و صنایع غذایی | متخصصان و کارشناسان علوم و صنایع غذایی | بازرسان و ممیزان اموال دولتی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | مدیران تولید صنعتی | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | کارشناسان تحلیل کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | بازرسان ترابری و حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی) | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | علوم کاربردی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | علوم | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | مدیریت و امور اداری | زیست‌شناسی | ریاضیات | اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | زیست‌شناسی | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | انعطاف‌پذیری در دسته‌بندی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | دید دور | قدرت تنه | استحکام و قدرت بدنی | هماهنگی میان اعضای بدن | چابکی انگشتان | ثبات دست و بازو | مرتب‌سازی اطلاعات | استدلال استقرایی | درک شفاهی</t>
+          <t>بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | استدلال قیاسی | حساسیت به مسئله | وضوح گفتار | بینایی دور | قدرت تنه | قدرت ایستا | هماهنگی چند عضو | مهارت انگشتان | ثبات دست و بازو | ترتیب‌دهی اطلاعات | استدلال استقرایی | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>محیط باز و مواجهه با شرایط جوی | استقلال در تصمیم‌گیری | تعیین اولویت‌ها و اهداف کاری | پیامدهای مهم خطای کاری | کار در محیط مسقف باز</t>
+          <t>آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فضای باز، در معرض تمام شرایط آب و هوایی | پیامد خطا | فضای باز، زیر سقف</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>بازرسان محصولات و فرآورده‌های کشاورزی | تکنسین‌های کشاورزی | کارگران مراقبت و نگهداری از حیوانات | ماموران کنترل و جمع‌آوری حیوانات | دانشمندان و کارشناسان علوم دامی | مربیان آموزش حیوانات | خریداران و کارگزاران خرید محصولات کشاورزی و دامی | مدیران امور کشاورزی و دامپروری | کارگران زراعت، نهالستان و گلخانه | کارگران مزارع پرورش دام، طیور و آبزیان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | صیادان و شکارچیان تجاری | دانشمندان و متخصصان علوم و صنایع غذایی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | قطعه‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی | کارگران کشتارگاه و بسته‌بندی گوشت | کارشناسان خاک‌شناسی و علوم زراعی | دامپزشکان | دستیاران دامپزشکی و مراقبان حیوانات آزمایشگاهی | تکنسین‌ها و کاردان‌های دامپزشکی</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | تکنسین‌های کشاورزی | مراقبان و نگهداران حیوانات | ماموران کنترل و ساماندهی حیوانات | متخصصان علوم دامی | مربیان و رام‌کنندگان حیوانات | خریداران و کارشناسان خرید محصولات کشاورزی | مدیران امور کشاورزی، دامپروری و شیلات | کارگران زراعت، نهالستان و گلخانه | کارگران پرورش دام، طیور و آبزیان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | صیادان، ماهیگیران و شکارچیان | متخصصان و کارشناسان علوم و صنایع غذایی | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | قصابان و بسته‌بندی‌کنندگان گوشت | متخصصان خاک‌شناسی و علوم گیاهی | دامپزشکان | دستیاران دامپزشکی و متصدیان نگهداری حیوانات آزمایشگاهی | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>چابکی دستی | دید نزدیک | انعطاف‌پذیری در دسته‌بندی | چابکی انگشتان | درک شفاهی</t>
+          <t>مهارت دستی | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | درک شفاهی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | بازرسان محصولات و فرآورده‌های کشاورزی | نانوایان و شیرینی‌پزان | اپراتورها و متصدیان تجهیزات شست‌وشو و اسیدشویی فلزات | تنظیم‌کنندگان و اپراتورهای دستگاه‌های سنگ‌شکنی و خردایش | تنظیم‌کنندگان و اپراتورهای دستگاه‌های برش و اسلایسر مواد | تنظیم‌کنندگان و اپراتورهای دستگاه‌های پرس، شکل‌دهی و تراکم مواد | کارگران زراعت، نهالستان و گلخانه | آماده‌سازان و مخلوط‌کنندگان مواد غذایی صنعتی | اپراتورها و متصدیان دیگ‌های پخت مواد غذایی صنعتی | تکنسین‌های علوم صنایع غذایی | اپراتورها و متصدیان دستگاه‌های بو دادن، برشته‌کاری و خشک‌کن مواد غذایی و توتون | کارگران خدماتی و جابجایی دستی بار | متصدیان درجه‌بندی و اندازه‌گیری الوار و گرده‌بینه | اپراتورهای بارگذاری و تخلیه ماشین‌آلات | قطعه‌کاران و پاک‌کنندگان گوشت، مرغ و ماهی | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | بسته‌بندهای دستی کالا | تنظیم‌کنندگان و اپراتورهای دستگاه‌های تفکیک، تصفیه، فیلتراسیون و تقطیر مواد | متصدیان توزین، سنجش و نمونه‌برداری</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | بازرسان محصولات و فرآورده‌های کشاورزی | نانوایان و شیرینی‌پزان | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | کارگران زراعت، نهالستان و گلخانه | تولیدکنندگان فرمولی و دسته‌ای مواد غذایی | اپراتورهای ماشین‌آلات پخت مواد غذایی | تکنسین‌های علوم و صنایع غذایی | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران جابه‌جایی دستی بار، کالا و مصالح | ارزیابان، ابعادبرداران و درجه‌بندی‌کنندگان الوار | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | برش‌کاران و پاک‌کنندگان گوشت، مرغ و آبزیان | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دقت در کنترل | هماهنگی میان اعضای بدن | دید نزدیک | ادراک عمق | دید دور | حساسیت به مسئله | جهت‌یابی پاسخ | کنترل سرعت | زمان واکنش | درک شفاهی | ثبات دست و بازو | چابکی دستی | بیان شفاهی | حساسیت شنوایی | قدرت تنه | استحکام و قدرت بدنی | وضوح گفتار | تشخیص گفتار | وسعت دامنه حرکتی | چابکی انگشتان | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی نزدیک | درک عمق | بینایی دور | حساسیت به مسئله | جهت‌گیری پاسخ | کنترل نرخ | زمان عکس‌العمل | درک شفاهی | ثبات دست و بازو | مهارت دستی | بیان شفاهی | حساسیت شنوایی | قدرت تنه | قدرت ایستا | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | مهارت انگشتان | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورهای نوار نقاله و خطوط انتقال مواد | تنظیم‌کنندگان و اپراتورهای دستگاه‌های سنگ‌شکنی و خردایش | تنظیم‌کنندگان و اپراتورهای دستگاه‌های برش و اسلایسر مواد | اپراتورهای ماشین‌آلات حفاری، بارگیری و دراگ‌لاین در معادن سطحی | تنظیم‌کنندگان و اپراتورهای دستگاه‌های تولید الیاف شیشه و سنتزی | تنظیم‌کنندگان و اپراتورهای دستگاه‌های پرس، شکل‌دهی و تراکم مواد | کارگران زراعت، نهالستان و گلخانه | مکانیک‌های ماشین‌آلات صنعتی | رانندگان تراکتور و لیفتراک‌های صنعتی | کارگران خدماتی و جابجایی دستی بار | اپراتورهای بارگذاری و تخلیه ماشین‌آلات | تعمیرکاران و تکنسین‌های نگهداری ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای دستگاه‌های فرز و صفحه تراش فلز و پلاستیک | مهندسان ماشین‌آلات سنگین و اپراتورهای تجهیزات عمرانی | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | بسته‌بندهای دستی کالا | اپراتورهای ماشین‌آلات آسفالت‌کاری و تراکم خاک | سم‌پاشان و کارشناسان کاربرد سموم دفع آفات نباتی | تنظیم‌کنندگان و اپراتورهای دستگاه‌های تفکیک، تصفیه، فیلتراسیون و تقطیر مواد | تنظیم‌کنندگان و اپراتورهای دستگاه‌های صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>اپراتورها و متصدیان نوار نقاله | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | کارگران زراعت، نهالستان و گلخانه | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | سم‌پاشان و متصدیان کاربرد آفت‌کش‌های نباتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
